--- a/data/pupil/3_processed/15_semantic_similarity/event/sub_1014_cosine_similarity.xlsx
+++ b/data/pupil/3_processed/15_semantic_similarity/event/sub_1014_cosine_similarity.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,10 +446,20 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Natalie Wood</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Grandfather Clocks</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Impatient Billionaire</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Dont Look</t>
         </is>
@@ -466,9 +476,15 @@
         <v>0.5167491436004639</v>
       </c>
       <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.3475861251354218</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.2147209793329239</v>
       </c>
     </row>
@@ -483,9 +499,15 @@
         <v>0.7112606763839722</v>
       </c>
       <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.356610894203186</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.115790106356144</v>
       </c>
     </row>
@@ -500,9 +522,15 @@
         <v>0.6107735633850098</v>
       </c>
       <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.2218195497989655</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>0.2319610714912415</v>
       </c>
     </row>
@@ -517,9 +545,15 @@
         <v>0.6492616534233093</v>
       </c>
       <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.4158441424369812</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>0.2663705348968506</v>
       </c>
     </row>
@@ -534,9 +568,15 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.4292865991592407</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.5408318638801575</v>
       </c>
     </row>
@@ -551,9 +591,15 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.6565271019935608</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
         <v>0.4981212019920349</v>
       </c>
     </row>
@@ -568,9 +614,15 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.4889043569564819</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>0.5103598237037659</v>
       </c>
     </row>
@@ -585,9 +637,15 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>0.7466098666191101</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
         <v>0.2572420835494995</v>
       </c>
     </row>
@@ -602,9 +660,15 @@
         <v>0.5607144236564636</v>
       </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>0.5351862907409668</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>0.6121017932891846</v>
       </c>
     </row>
@@ -619,9 +683,15 @@
         <v>0.3620789349079132</v>
       </c>
       <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.4772910177707672</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -636,9 +706,15 @@
         <v>0.3708817064762115</v>
       </c>
       <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
         <v>0.355279803276062</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -653,9 +729,15 @@
         <v>0.7685636281967163</v>
       </c>
       <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.5551944971084595</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -670,9 +752,15 @@
         <v>0.653389573097229</v>
       </c>
       <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
         <v>0.4868383407592773</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -687,9 +775,15 @@
         <v>0.5609975457191467</v>
       </c>
       <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
         <v>0.3740340173244476</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
         <v>0.293252170085907</v>
       </c>
     </row>
@@ -704,9 +798,15 @@
         <v>0.3567264676094055</v>
       </c>
       <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
         <v>0.3843646645545959</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
         <v>0.2242860049009323</v>
       </c>
     </row>
@@ -724,6 +824,12 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
         <v>0.2908750474452972</v>
       </c>
     </row>
@@ -738,9 +844,15 @@
         <v>0.6121939420700073</v>
       </c>
       <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
         <v>0.4245063662528992</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
         <v>0.2413997948169708</v>
       </c>
     </row>
@@ -755,9 +867,13 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
         <v>0.5396136045455933</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -772,9 +888,13 @@
         <v>0.5003503561019897</v>
       </c>
       <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
         <v>0.579806923866272</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -789,9 +909,13 @@
         <v>0.5075818300247192</v>
       </c>
       <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
         <v>0.338223397731781</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
         <v>0.4598760008811951</v>
       </c>
     </row>
@@ -807,6 +931,10 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
         <v>-0.04441946372389793</v>
       </c>
     </row>
@@ -819,9 +947,13 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
         <v>0.4802228808403015</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
         <v>0.5837050676345825</v>
       </c>
     </row>
@@ -834,9 +966,13 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
         <v>0.7353578209877014</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
         <v>0.008153228089213371</v>
       </c>
     </row>
@@ -847,9 +983,13 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
         <v>0.6771414279937744</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
         <v>0.4777448773384094</v>
       </c>
     </row>
@@ -860,9 +1000,13 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
         <v>0.5912452936172485</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
         <v>0.1744225025177002</v>
       </c>
     </row>
@@ -873,9 +1017,13 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
         <v>0.2567515969276428</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="n">
         <v>0.1610338985919952</v>
       </c>
     </row>
@@ -886,9 +1034,13 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
         <v>0.29742631316185</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -899,9 +1051,13 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
         <v>0.3794603645801544</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -912,9 +1068,13 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
         <v>0.4752022624015808</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -924,8 +1084,12 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="n">
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -935,8 +1099,12 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="n">
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -946,8 +1114,12 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="n">
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -957,8 +1129,12 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="n">
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -968,8 +1144,12 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="n">
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="n">
         <v>0.4691768288612366</v>
       </c>
     </row>
@@ -979,8 +1159,12 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="n">
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="n">
         <v>0.663501501083374</v>
       </c>
     </row>
@@ -990,8 +1174,12 @@
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="n">
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="n">
         <v>0.05560113862156868</v>
       </c>
     </row>
@@ -1001,8 +1189,12 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="n">
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
         <v>0.15046526491642</v>
       </c>
     </row>
@@ -1012,8 +1204,12 @@
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="n">
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
         <v>0.009374251589179039</v>
       </c>
     </row>
@@ -1023,8 +1219,12 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="n">
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1034,8 +1234,12 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="n">
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="n">
         <v>0.4221961498260498</v>
       </c>
     </row>
@@ -1045,10 +1249,196 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="n">
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="n">
         <v>0.5427722334861755</v>
       </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
